--- a/data/trans_orig/Q25_A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años desde que dejó de fumar</t>
+          <t>Tiempo medio en años desde que dejó de fumar (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,46</t>
+          <t>1,11; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,68</t>
+          <t>0,96; 2,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,0</t>
+          <t>0,17; 1,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,16</t>
+          <t>0,86; 2,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,68</t>
+          <t>1,14; 2,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,08</t>
+          <t>1,41; 2,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,72</t>
+          <t>1,21; 3,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,37</t>
+          <t>1,11; 2,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,33</t>
+          <t>1,18; 2,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,5</t>
+          <t>1,32; 2,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,05</t>
+          <t>0,93; 2,89</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,11</t>
+          <t>3,17; 6,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,67</t>
+          <t>2,28; 3,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 4,85</t>
+          <t>3,3; 4,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,18</t>
+          <t>2,22; 6,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,22</t>
+          <t>2,81; 4,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,05</t>
+          <t>3,21; 5,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,74</t>
+          <t>2,81; 4,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,21</t>
+          <t>3,42; 7,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,47</t>
+          <t>3,07; 4,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,12</t>
+          <t>2,86; 4,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 4,41</t>
+          <t>3,27; 4,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,08</t>
+          <t>3,31; 5,99</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,98</t>
+          <t>4,82; 6,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 6,89</t>
+          <t>4,85; 6,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,64</t>
+          <t>4,52; 6,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 9,37</t>
+          <t>5,81; 9,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,51</t>
+          <t>6,75; 9,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,91</t>
+          <t>6,63; 8,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,24</t>
+          <t>5,9; 8,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 10,18</t>
+          <t>6,93; 10,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 7,7</t>
+          <t>5,87; 7,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,56</t>
+          <t>6,05; 7,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,15</t>
+          <t>5,56; 7,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,23</t>
+          <t>6,7; 9,16</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,48</t>
+          <t>6,23; 8,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,05</t>
+          <t>8,23; 11,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 11,38</t>
+          <t>8,66; 11,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 11,68</t>
+          <t>2,69; 11,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,69</t>
+          <t>6,23; 9,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,89</t>
+          <t>8,54; 12,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 11,93</t>
+          <t>8,8; 12,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,57</t>
+          <t>11,01; 14,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,33</t>
+          <t>6,55; 8,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,83</t>
+          <t>8,63; 10,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,14</t>
+          <t>9,13; 11,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 12,19</t>
+          <t>3,08; 12,18</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 13,14</t>
+          <t>10,04; 13,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,72; 13,98</t>
+          <t>10,54; 13,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 14,96</t>
+          <t>11,58; 14,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 16,92</t>
+          <t>13,71; 17,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,1</t>
+          <t>7,38; 15,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,72</t>
+          <t>7,59; 11,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,64; 13,13</t>
+          <t>8,47; 13,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 16,21</t>
+          <t>12,82; 16,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 12,95</t>
+          <t>9,99; 12,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 12,86</t>
+          <t>10,38; 12,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 13,9</t>
+          <t>11,2; 13,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,9; 16,38</t>
+          <t>13,84; 16,31</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,14; 15,8</t>
+          <t>12,28; 15,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,99; 17,44</t>
+          <t>13,91; 17,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,2; 17,87</t>
+          <t>14,13; 17,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,92; 20,11</t>
+          <t>16,85; 20,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,61</t>
+          <t>5,32; 12,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 22,05</t>
+          <t>5,32; 24,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,77; 22,0</t>
+          <t>12,22; 22,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,82; 25,2</t>
+          <t>16,79; 25,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,8; 15,31</t>
+          <t>11,75; 15,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,59; 17,14</t>
+          <t>13,66; 17,19</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,37; 17,89</t>
+          <t>14,33; 17,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,37; 20,51</t>
+          <t>17,52; 20,42</t>
         </is>
       </c>
     </row>
@@ -1556,32 +1556,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,13; 19,82</t>
+          <t>16,12; 19,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,4; 24,44</t>
+          <t>19,46; 24,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,06; 23,07</t>
+          <t>19,1; 23,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,88; 27,9</t>
+          <t>23,91; 27,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,88; 27,65</t>
+          <t>10,62; 29,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,65; 31,45</t>
+          <t>8,58; 33,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,19; 32,47</t>
+          <t>21,43; 31,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,07; 19,78</t>
+          <t>16,16; 19,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,34; 23,99</t>
+          <t>19,38; 24,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19,51; 24,06</t>
+          <t>19,34; 23,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,13; 27,85</t>
+          <t>24,21; 27,91</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,55</t>
+          <t>10,16; 11,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1706,52 +1706,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,84; 13,43</t>
+          <t>11,78; 13,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,69</t>
+          <t>6,12; 16,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 7,71</t>
+          <t>5,96; 7,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,49</t>
+          <t>6,97; 8,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,99; 9,96</t>
+          <t>8,0; 10,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,76; 14,09</t>
+          <t>11,83; 14,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,07; 10,24</t>
+          <t>9,11; 10,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,08; 11,29</t>
+          <t>10,06; 11,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,7; 12,03</t>
+          <t>10,7; 11,98</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,35; 15,41</t>
+          <t>7,55; 15,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25_A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q25_A_R-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,15</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>1,71</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1,13; 3,41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,95; 2,63</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,69; 1,85</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,17; 1,69</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,86; 2,15</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,13; 2,67</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1,48; 3,1</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1,11; 3,5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,96; 2,7</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,67; 1,8</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 1,66</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,86; 2,13</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 2,7</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,41; 2,99</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 3,86</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,42</t>
+          <t>1,13; 2,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,29</t>
+          <t>1,21; 2,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,45</t>
+          <t>1,28; 2,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,89</t>
+          <t>1,0; 3,12</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,14</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>4,82</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,06</t>
+          <t>3,23; 5,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,7</t>
+          <t>2,24; 3,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,89</t>
+          <t>3,3; 4,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,01</t>
+          <t>2,23; 5,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,25</t>
+          <t>2,77; 4,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,01</t>
+          <t>3,19; 5,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,67</t>
+          <t>2,9; 4,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,04</t>
+          <t>4,0; 7,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 4,4</t>
+          <t>3,07; 4,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,13</t>
+          <t>2,89; 4,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,53</t>
+          <t>3,26; 4,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,99</t>
+          <t>3,69; 6,18</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,54</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,79</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,91</t>
+          <t>4,83; 6,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,97</t>
+          <t>4,85; 6,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,66</t>
+          <t>4,54; 6,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,31</t>
+          <t>5,94; 9,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 9,58</t>
+          <t>6,69; 9,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,89</t>
+          <t>6,64; 8,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,32</t>
+          <t>5,92; 8,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 10,39</t>
+          <t>6,45; 9,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,62</t>
+          <t>5,94; 7,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,6</t>
+          <t>6,03; 7,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,11</t>
+          <t>5,61; 7,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,16</t>
+          <t>6,64; 9,06</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>11,47</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,7</t>
+          <t>12,47</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,3</t>
+          <t>11,92</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,55</t>
+          <t>6,24; 8,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 11,11</t>
+          <t>8,28; 11,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 11,45</t>
+          <t>8,59; 11,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 11,6</t>
+          <t>10,1; 13,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,76</t>
+          <t>6,15; 9,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 12,11</t>
+          <t>8,32; 11,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,04</t>
+          <t>8,63; 11,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,01; 14,38</t>
+          <t>11,03; 14,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,37</t>
+          <t>6,6; 8,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 10,9</t>
+          <t>8,59; 10,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 11,17</t>
+          <t>9,13; 11,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 12,18</t>
+          <t>10,85; 13,02</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,32</t>
+          <t>15,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,41</t>
+          <t>14,58</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,99</t>
+          <t>14,91</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,04; 13,13</t>
+          <t>10,28; 13,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 13,82</t>
+          <t>10,61; 13,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,58; 14,95</t>
+          <t>11,66; 15,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,71; 17,03</t>
+          <t>13,55; 16,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,38; 15,3</t>
+          <t>7,25; 15,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,78</t>
+          <t>7,65; 11,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,1</t>
+          <t>8,75; 13,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,82; 16,19</t>
+          <t>12,9; 16,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,99; 12,76</t>
+          <t>10,21; 12,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 12,94</t>
+          <t>10,21; 13,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,84</t>
+          <t>11,08; 13,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,84; 16,31</t>
+          <t>13,74; 16,11</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,49</t>
+          <t>18,33</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,11</t>
+          <t>19,4</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,85</t>
+          <t>18,56</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,28; 15,73</t>
+          <t>12,06; 15,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,91; 17,49</t>
+          <t>14,01; 17,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,13; 17,95</t>
+          <t>14,24; 17,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,85; 20,04</t>
+          <t>16,93; 19,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,43</t>
+          <t>5,39; 13,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 24,88</t>
+          <t>4,82; 22,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,22; 22,3</t>
+          <t>11,67; 22,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,79; 25,38</t>
+          <t>16,18; 22,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,75; 15,16</t>
+          <t>11,8; 15,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 17,19</t>
+          <t>13,6; 17,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,33; 17,94</t>
+          <t>14,21; 17,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,52; 20,42</t>
+          <t>17,3; 19,99</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>25,77</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>25,4</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,9</t>
+          <t>25,73</t>
         </is>
       </c>
     </row>
@@ -1556,32 +1556,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,12; 19,75</t>
+          <t>16,08; 19,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,46; 24,17</t>
+          <t>19,52; 24,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,1; 23,1</t>
+          <t>18,98; 23,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23,91; 27,7</t>
+          <t>23,84; 27,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,62; 29,09</t>
+          <t>10,36; 27,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 33,21</t>
+          <t>8,17; 32,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,43; 31,79</t>
+          <t>20,56; 31,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,16; 19,74</t>
+          <t>16,03; 19,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,38; 24,01</t>
+          <t>19,22; 24,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19,34; 23,84</t>
+          <t>19,31; 24,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,21; 27,91</t>
+          <t>24,06; 27,6</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12,17</t>
+          <t>16,25</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>12,71</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,37</t>
+          <t>14,99</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,16; 11,62</t>
+          <t>10,16; 11,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,28; 12,97</t>
+          <t>11,25; 12,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,78; 13,46</t>
+          <t>11,88; 13,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,12; 16,65</t>
+          <t>15,37; 17,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,65</t>
+          <t>5,98; 7,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,97; 8,6</t>
+          <t>6,84; 8,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 10,1</t>
+          <t>7,96; 9,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,83; 14,03</t>
+          <t>11,68; 13,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,11; 10,31</t>
+          <t>9,11; 10,29</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,06; 11,27</t>
+          <t>10,03; 11,31</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,98</t>
+          <t>10,7; 12,01</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,33</t>
+          <t>14,35; 15,77</t>
         </is>
       </c>
     </row>
